--- a/漢字（かんじ）/z.xlsx
+++ b/漢字（かんじ）/z.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ざ" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
   <si>
     <t>仮名</t>
   </si>
@@ -305,6 +305,13 @@
 依存症｜いぞんしょう</t>
     </r>
   </si>
+  <si>
+    <t>俗</t>
+  </si>
+  <si>
+    <t>風俗｜ふうぞく
+風俗画｜ふうぞくが</t>
+  </si>
 </sst>
 </file>
 
@@ -316,7 +323,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,13 +342,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -797,158 +797,161 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1536,7 +1539,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="21.2222222222222" customWidth="1"/>
@@ -1642,6 +1645,17 @@
         <v>63</v>
       </c>
     </row>
+    <row r="10" ht="27.6" spans="1:4">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/漢字（かんじ）/z.xlsx
+++ b/漢字（かんじ）/z.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ざ" sheetId="1" r:id="rId1"/>
@@ -168,6 +168,7 @@
 事前｜じぜん
 直前｜ちょくぜん
 前後｜ぜんご
+前非｜ぜんぴ
 前後左右｜ぜんごさゆう</t>
   </si>
   <si>
@@ -1475,7 +1476,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" ht="90" spans="1:3">
+    <row r="3" ht="108" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
